--- a/math-sdk/games/smukiez_tag_run/library/smukiez_tag_run_full_statistics.xlsx
+++ b/math-sdk/games/smukiez_tag_run/library/smukiez_tag_run_full_statistics.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="145">
   <si>
     <t>Win Ranges</t>
   </si>
@@ -84,153 +84,141 @@
     <t>basegame</t>
   </si>
   <si>
-    <t>1.006</t>
-  </si>
-  <si>
-    <t>1.418</t>
-  </si>
-  <si>
-    <t>11179.207</t>
-  </si>
-  <si>
-    <t>72269.886</t>
-  </si>
-  <si>
-    <t>4.085</t>
-  </si>
-  <si>
-    <t>11259.946</t>
-  </si>
-  <si>
-    <t>65492.532</t>
-  </si>
-  <si>
-    <t>29.15</t>
-  </si>
-  <si>
-    <t>3947.895</t>
-  </si>
-  <si>
-    <t>24228.908</t>
-  </si>
-  <si>
-    <t>783.797</t>
-  </si>
-  <si>
-    <t>2596.518</t>
-  </si>
-  <si>
-    <t>20433.149</t>
-  </si>
-  <si>
-    <t>631.375</t>
-  </si>
-  <si>
-    <t>1173.906</t>
-  </si>
-  <si>
-    <t>8653.914</t>
-  </si>
-  <si>
-    <t>209.414</t>
-  </si>
-  <si>
-    <t>665.373</t>
-  </si>
-  <si>
-    <t>4904.226</t>
-  </si>
-  <si>
-    <t>187.839</t>
-  </si>
-  <si>
-    <t>536.242</t>
-  </si>
-  <si>
-    <t>2763.252</t>
-  </si>
-  <si>
-    <t>405.574</t>
-  </si>
-  <si>
-    <t>3712.24</t>
-  </si>
-  <si>
-    <t>6571.436</t>
-  </si>
-  <si>
-    <t>3232.094</t>
-  </si>
-  <si>
-    <t>202365.045</t>
-  </si>
-  <si>
-    <t>36974.362</t>
-  </si>
-  <si>
-    <t>274444.898</t>
-  </si>
-  <si>
-    <t>986477.888</t>
-  </si>
-  <si>
-    <t>34828.451</t>
-  </si>
-  <si>
-    <t>354879.711</t>
-  </si>
-  <si>
-    <t>807931.812</t>
-  </si>
-  <si>
-    <t>56801.502</t>
-  </si>
-  <si>
-    <t>779941.793</t>
-  </si>
-  <si>
-    <t>893683.408</t>
-  </si>
-  <si>
-    <t>135959.059</t>
-  </si>
-  <si>
-    <t>3122011.695</t>
-  </si>
-  <si>
-    <t>1408940.255</t>
-  </si>
-  <si>
-    <t>1273779.216</t>
-  </si>
-  <si>
-    <t>10507658.508</t>
-  </si>
-  <si>
-    <t>1242529.326</t>
-  </si>
-  <si>
-    <t>1314581.732</t>
+    <t>1.005</t>
+  </si>
+  <si>
+    <t>1.669</t>
+  </si>
+  <si>
+    <t>19486.227</t>
+  </si>
+  <si>
+    <t>87638.546</t>
+  </si>
+  <si>
+    <t>2.584</t>
+  </si>
+  <si>
+    <t>16432.68</t>
+  </si>
+  <si>
+    <t>102672.085</t>
+  </si>
+  <si>
+    <t>1232.955</t>
+  </si>
+  <si>
+    <t>7821.797</t>
+  </si>
+  <si>
+    <t>13744.713</t>
+  </si>
+  <si>
+    <t>689.727</t>
+  </si>
+  <si>
+    <t>3964.421</t>
+  </si>
+  <si>
+    <t>15161.816</t>
+  </si>
+  <si>
+    <t>571.57</t>
+  </si>
+  <si>
+    <t>1982.67</t>
+  </si>
+  <si>
+    <t>3593.677</t>
+  </si>
+  <si>
+    <t>427.478</t>
+  </si>
+  <si>
+    <t>1778.03</t>
+  </si>
+  <si>
+    <t>759.45</t>
+  </si>
+  <si>
+    <t>191.873</t>
+  </si>
+  <si>
+    <t>6268.105</t>
+  </si>
+  <si>
+    <t>1214.542</t>
+  </si>
+  <si>
+    <t>542.809</t>
+  </si>
+  <si>
+    <t>2300.584</t>
+  </si>
+  <si>
+    <t>16042.363</t>
+  </si>
+  <si>
+    <t>1894.4</t>
+  </si>
+  <si>
+    <t>38168.906</t>
+  </si>
+  <si>
+    <t>453506.005</t>
+  </si>
+  <si>
+    <t>77826.885</t>
+  </si>
+  <si>
+    <t>23150.342</t>
+  </si>
+  <si>
+    <t>101626.065</t>
+  </si>
+  <si>
+    <t>147034.641</t>
+  </si>
+  <si>
+    <t>23138.554</t>
+  </si>
+  <si>
+    <t>124242.464</t>
+  </si>
+  <si>
+    <t>649792.944</t>
+  </si>
+  <si>
+    <t>22947.898</t>
+  </si>
+  <si>
+    <t>105918.458</t>
   </si>
   <si>
     <t>NaN</t>
   </si>
   <si>
-    <t>13917251.43</t>
-  </si>
-  <si>
-    <t>7059801.21</t>
-  </si>
-  <si>
-    <t>4370016949.053</t>
+    <t>99310.275</t>
+  </si>
+  <si>
+    <t>718095.375</t>
+  </si>
+  <si>
+    <t>1286439.715</t>
+  </si>
+  <si>
+    <t>732977.859</t>
+  </si>
+  <si>
+    <t>5804599.695</t>
+  </si>
+  <si>
+    <t>2885715.277</t>
   </si>
   <si>
     <t>HIT RATES</t>
   </si>
   <si>
-    <t>W</t>
-  </si>
-  <si>
     <t>C3</t>
   </si>
   <si>
@@ -321,145 +309,148 @@
     <t>{'symbol': 'scatter'}</t>
   </si>
   <si>
-    <t>12.571410289309322</t>
-  </si>
-  <si>
-    <t>7831</t>
-  </si>
-  <si>
-    <t>91.41891857784553</t>
+    <t>12.054945788609068</t>
+  </si>
+  <si>
+    <t>7822</t>
+  </si>
+  <si>
+    <t>104.17081473307162</t>
   </si>
   <si>
     <t>{'symbol': 'scatter_extreme'}</t>
   </si>
   <si>
-    <t>47.34105930861061</t>
+    <t>43.273240821331676</t>
   </si>
   <si>
     <t>2100</t>
   </si>
   <si>
-    <t>89.23047795031266</t>
-  </si>
-  <si>
-    <t>295.626</t>
-  </si>
-  <si>
-    <t>64.393</t>
-  </si>
-  <si>
-    <t>76.356</t>
-  </si>
-  <si>
-    <t>27.047</t>
-  </si>
-  <si>
-    <t>17.101</t>
-  </si>
-  <si>
-    <t>7.423</t>
-  </si>
-  <si>
-    <t>2.402</t>
-  </si>
-  <si>
-    <t>11.293</t>
-  </si>
-  <si>
-    <t>9.672</t>
-  </si>
-  <si>
-    <t>18.783</t>
-  </si>
-  <si>
-    <t>23.943</t>
-  </si>
-  <si>
-    <t>37.265</t>
-  </si>
-  <si>
-    <t>141.888</t>
-  </si>
-  <si>
-    <t>2462.204</t>
-  </si>
-  <si>
-    <t>5553.875</t>
-  </si>
-  <si>
-    <t>12635.542</t>
+    <t>64.2297428372789</t>
+  </si>
+  <si>
+    <t>182.601</t>
+  </si>
+  <si>
+    <t>34.953</t>
+  </si>
+  <si>
+    <t>47.335</t>
+  </si>
+  <si>
+    <t>14.324</t>
+  </si>
+  <si>
+    <t>8.334</t>
+  </si>
+  <si>
+    <t>4.134</t>
+  </si>
+  <si>
+    <t>3.071</t>
+  </si>
+  <si>
+    <t>24.801</t>
+  </si>
+  <si>
+    <t>19.853</t>
+  </si>
+  <si>
+    <t>104.813</t>
+  </si>
+  <si>
+    <t>30.261</t>
+  </si>
+  <si>
+    <t>31.033</t>
+  </si>
+  <si>
+    <t>48.836</t>
+  </si>
+  <si>
+    <t>906.486</t>
+  </si>
+  <si>
+    <t>3032.535</t>
+  </si>
+  <si>
+    <t>12500.0</t>
   </si>
   <si>
     <t>1.0</t>
   </si>
   <si>
-    <t>20000</t>
-  </si>
-  <si>
-    <t>9649.999999665979</t>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>9650.00000001939</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>1084.835</t>
-  </si>
-  <si>
-    <t>292.732</t>
-  </si>
-  <si>
-    <t>279.65</t>
-  </si>
-  <si>
-    <t>107.894</t>
-  </si>
-  <si>
-    <t>60.69</t>
-  </si>
-  <si>
-    <t>25.679</t>
-  </si>
-  <si>
-    <t>5.107</t>
-  </si>
-  <si>
-    <t>2.175</t>
-  </si>
-  <si>
-    <t>13.773</t>
-  </si>
-  <si>
-    <t>173.469</t>
-  </si>
-  <si>
-    <t>15.315</t>
-  </si>
-  <si>
-    <t>56.184</t>
-  </si>
-  <si>
-    <t>25.873</t>
-  </si>
-  <si>
-    <t>33.682</t>
-  </si>
-  <si>
-    <t>24.264</t>
-  </si>
-  <si>
-    <t>1287.824</t>
-  </si>
-  <si>
-    <t>2.575189680770707</t>
-  </si>
-  <si>
-    <t>7654</t>
-  </si>
-  <si>
-    <t>37915.980359305904</t>
-  </si>
-  <si>
-    <t>38599.99999992138</t>
+    <t>1984.67</t>
+  </si>
+  <si>
+    <t>128.663</t>
+  </si>
+  <si>
+    <t>156.678</t>
+  </si>
+  <si>
+    <t>36.0</t>
+  </si>
+  <si>
+    <t>18.781</t>
+  </si>
+  <si>
+    <t>7.428</t>
+  </si>
+  <si>
+    <t>2.556</t>
+  </si>
+  <si>
+    <t>6.512</t>
+  </si>
+  <si>
+    <t>12.441</t>
+  </si>
+  <si>
+    <t>274.856</t>
+  </si>
+  <si>
+    <t>41.953</t>
+  </si>
+  <si>
+    <t>161.835</t>
+  </si>
+  <si>
+    <t>32.796</t>
+  </si>
+  <si>
+    <t>40.897</t>
+  </si>
+  <si>
+    <t>18.139</t>
+  </si>
+  <si>
+    <t>1351.257</t>
+  </si>
+  <si>
+    <t>2.571717157924888</t>
+  </si>
+  <si>
+    <t>2879</t>
+  </si>
+  <si>
+    <t>42404.70288758986</t>
+  </si>
+  <si>
+    <t>7500</t>
+  </si>
+  <si>
+    <t>38599.99999995804</t>
   </si>
 </sst>
 </file>
@@ -791,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -817,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="M1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -825,7 +816,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1.43</v>
+        <v>1.681</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -854,10 +845,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>4.09</v>
+        <v>2.587</v>
       </c>
       <c r="C3">
-        <v>0.1229964743827526</v>
+        <v>0.1599731528640545</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
@@ -875,7 +866,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>29939</v>
+        <v>49447</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -883,10 +874,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>29.172</v>
+        <v>1573.472</v>
       </c>
       <c r="C4">
-        <v>0.03444463484786096</v>
+        <v>0.0009060581506196012</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
@@ -904,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>9693</v>
+        <v>6774</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -912,10 +903,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>699.198</v>
+        <v>664.681</v>
       </c>
       <c r="C5">
-        <v>0.004723146199117841</v>
+        <v>0.004997261077113005</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -933,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>11022</v>
+        <v>4909</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -941,10 +932,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>501.108</v>
+        <v>486.895</v>
       </c>
       <c r="C6">
-        <v>0.01477988179743758</v>
+        <v>0.01485339454406566</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -962,7 +953,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>4759</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -970,10 +961,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>174.975</v>
+        <v>321.142</v>
       </c>
       <c r="C7">
-        <v>0.0855684281656066</v>
+        <v>0.04715464181045158</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -991,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>3047</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -999,10 +990,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>141.847</v>
+        <v>142.67</v>
       </c>
       <c r="C8">
-        <v>0.2343536257671697</v>
+        <v>0.2264105623206348</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -1020,7 +1011,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>2615</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1028,10 +1019,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>212.699</v>
+        <v>348.517</v>
       </c>
       <c r="C9">
-        <v>0.3204577268505139</v>
+        <v>0.1897458436351959</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -1049,7 +1040,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>1155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1057,10 +1048,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>1368.083</v>
+        <v>975.729</v>
       </c>
       <c r="C10">
-        <v>0.09128572862535574</v>
+        <v>0.1380567251132152</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -1078,7 +1069,7 @@
         <v>11</v>
       </c>
       <c r="M10">
-        <v>658</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1086,10 +1077,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>28199.843</v>
+        <v>24240.421</v>
       </c>
       <c r="C11">
-        <v>0.008323296291975979</v>
+        <v>0.0105143086451506</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -1107,7 +1098,7 @@
         <v>12</v>
       </c>
       <c r="M11">
-        <v>249</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1115,10 +1106,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>30568.343</v>
+        <v>16712.062</v>
       </c>
       <c r="C12">
-        <v>0.01254523938675372</v>
+        <v>0.02248473713758386</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -1136,7 +1127,7 @@
         <v>13</v>
       </c>
       <c r="M12">
-        <v>278</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1144,10 +1135,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>49689.334</v>
+        <v>18937.37</v>
       </c>
       <c r="C13">
-        <v>0.01345801280012425</v>
+        <v>0.03908362765438808</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
@@ -1165,7 +1156,7 @@
         <v>14</v>
       </c>
       <c r="M13">
-        <v>239</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1173,10 +1164,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>113708.386</v>
+        <v>18861.447</v>
       </c>
       <c r="C14">
-        <v>0.01125388867696271</v>
+        <v>0.0736963124324965</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -1194,7 +1185,7 @@
         <v>15</v>
       </c>
       <c r="M14">
-        <v>228</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1202,10 +1193,10 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>628935.8050000001</v>
+        <v>87244.625</v>
       </c>
       <c r="C15">
-        <v>0.003870358850428302</v>
+        <v>0.02725694624635426</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -1217,13 +1208,13 @@
         <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L15" t="s">
         <v>16</v>
       </c>
       <c r="M15">
-        <v>102</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1231,28 +1222,28 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>642526.959</v>
+        <v>484865.18</v>
       </c>
       <c r="C16">
-        <v>0.005939556586444375</v>
+        <v>0.007866428141530053</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" t="s">
         <v>63</v>
       </c>
-      <c r="H16" t="s">
-        <v>64</v>
-      </c>
       <c r="I16" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L16" t="s">
         <v>17</v>
       </c>
       <c r="M16">
-        <v>142</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1260,483 +1251,483 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>5000019.393</v>
+        <v>2500000.859</v>
       </c>
       <c r="C17">
-        <v>0.001000080949559561</v>
+        <v>0.002000589015724829</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I17" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="L17" t="s">
         <v>18</v>
       </c>
       <c r="M17">
-        <v>874</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M21" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="B22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1162.92</v>
       </c>
       <c r="C23">
-        <v>735.66</v>
+        <v>254.02</v>
       </c>
       <c r="D23">
-        <v>317.01</v>
+        <v>801.45</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I23">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="J23">
-        <v>318</v>
+        <v>130</v>
       </c>
       <c r="M23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>132.7</v>
       </c>
       <c r="O23">
-        <v>95.59999999999999</v>
+        <v>113.5</v>
       </c>
       <c r="P23">
-        <v>130.7</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B24">
-        <v>5638.13</v>
+        <v>1166.03</v>
       </c>
       <c r="C24">
-        <v>2481.12</v>
+        <v>1226.26</v>
       </c>
       <c r="D24">
-        <v>2005.88</v>
+        <v>290.41</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H24">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="I24">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="J24">
-        <v>51</v>
+        <v>345</v>
       </c>
       <c r="M24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N24">
-        <v>25.2</v>
+        <v>249.7</v>
       </c>
       <c r="O24">
-        <v>162.2</v>
+        <v>179.1</v>
       </c>
       <c r="P24">
-        <v>108.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B25">
-        <v>5553.08</v>
+        <v>231.67</v>
       </c>
       <c r="C25">
-        <v>3720.71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D25">
-        <v>1008.84</v>
+        <v>39.99</v>
       </c>
       <c r="G25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H25">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="I25">
-        <v>37</v>
+        <v>523</v>
       </c>
       <c r="J25">
-        <v>109</v>
+        <v>2028</v>
       </c>
       <c r="M25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N25">
-        <v>55.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O25">
-        <v>64</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="P25">
-        <v>20.9</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B26">
-        <v>1662.77</v>
+        <v>136.76</v>
       </c>
       <c r="C26">
-        <v>679.41</v>
+        <v>44.31</v>
       </c>
       <c r="D26">
-        <v>145.6</v>
+        <v>15.35</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H26">
-        <v>59</v>
+        <v>458</v>
       </c>
       <c r="I26">
-        <v>154</v>
+        <v>1493</v>
       </c>
       <c r="J26">
-        <v>673</v>
+        <v>5696</v>
       </c>
       <c r="M26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N26">
-        <v>172.8</v>
+        <v>61</v>
       </c>
       <c r="O26">
-        <v>180.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="P26">
-        <v>112.1</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B27">
-        <v>237.35</v>
+        <v>99.02</v>
       </c>
       <c r="C27">
-        <v>97.84</v>
+        <v>38.9</v>
       </c>
       <c r="D27">
-        <v>25.66</v>
+        <v>18.68</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H27">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="I27">
-        <v>939</v>
+        <v>1407</v>
       </c>
       <c r="J27">
-        <v>3845</v>
+        <v>4673</v>
       </c>
       <c r="M27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N27">
-        <v>123.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O27">
-        <v>87.7</v>
+        <v>80.3</v>
       </c>
       <c r="P27">
-        <v>107.3</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28">
-        <v>285.79</v>
+        <v>95.87</v>
       </c>
       <c r="C28">
-        <v>115.49</v>
+        <v>46.62</v>
       </c>
       <c r="D28">
-        <v>32.28</v>
+        <v>16.53</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H28">
-        <v>330</v>
+        <v>449</v>
       </c>
       <c r="I28">
-        <v>802</v>
+        <v>1342</v>
       </c>
       <c r="J28">
-        <v>3067</v>
+        <v>5072</v>
       </c>
       <c r="M28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N28">
-        <v>67.7</v>
+        <v>85.3</v>
       </c>
       <c r="O28">
-        <v>76.7</v>
+        <v>60.9</v>
       </c>
       <c r="P28">
-        <v>95.3</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B29">
-        <v>279.1</v>
+        <v>142.11</v>
       </c>
       <c r="C29">
-        <v>133.49</v>
+        <v>40.23</v>
       </c>
       <c r="D29">
-        <v>28.81</v>
+        <v>16.22</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H29">
-        <v>338</v>
+        <v>418</v>
       </c>
       <c r="I29">
-        <v>774</v>
+        <v>1421</v>
       </c>
       <c r="J29">
-        <v>3396</v>
+        <v>5709</v>
       </c>
       <c r="M29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N29">
-        <v>52.4</v>
+        <v>54.3</v>
       </c>
       <c r="O29">
-        <v>69.2</v>
+        <v>69</v>
       </c>
       <c r="P29">
-        <v>96.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B30">
-        <v>314.16</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="C30">
-        <v>123.14</v>
+        <v>44.89</v>
       </c>
       <c r="D30">
-        <v>25.79</v>
+        <v>16.9</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H30">
-        <v>317</v>
+        <v>456</v>
       </c>
       <c r="I30">
-        <v>820</v>
+        <v>1460</v>
       </c>
       <c r="J30">
-        <v>3707</v>
+        <v>5509</v>
       </c>
       <c r="M30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N30">
-        <v>60.6</v>
+        <v>87.2</v>
       </c>
       <c r="O30">
-        <v>69</v>
+        <v>70.7</v>
       </c>
       <c r="P30">
-        <v>92.09999999999999</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B31">
-        <v>320.67</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="C31">
-        <v>118.88</v>
+        <v>34.86</v>
       </c>
       <c r="D31">
-        <v>27.1</v>
+        <v>18.7</v>
       </c>
       <c r="G31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H31">
-        <v>330</v>
+        <v>406</v>
       </c>
       <c r="I31">
-        <v>819</v>
+        <v>1458</v>
       </c>
       <c r="J31">
-        <v>3620</v>
+        <v>4680</v>
       </c>
       <c r="M31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N31">
-        <v>78.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="O31">
-        <v>90.7</v>
+        <v>75.7</v>
       </c>
       <c r="P31">
-        <v>97.3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B32">
-        <v>298.45</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="C32">
-        <v>138.51</v>
+        <v>46.42</v>
       </c>
       <c r="D32">
-        <v>32.89</v>
+        <v>16.79</v>
       </c>
       <c r="G32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H32">
-        <v>308</v>
+        <v>426</v>
       </c>
       <c r="I32">
-        <v>723</v>
+        <v>1427</v>
       </c>
       <c r="J32">
-        <v>2993</v>
+        <v>5402</v>
       </c>
       <c r="M32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N32">
-        <v>36.8</v>
+        <v>73.5</v>
       </c>
       <c r="O32">
-        <v>54.3</v>
+        <v>94.8</v>
       </c>
       <c r="P32">
-        <v>71.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B33">
-        <v>288.37</v>
+        <v>118.3</v>
       </c>
       <c r="C33">
-        <v>124.97</v>
+        <v>44.29</v>
       </c>
       <c r="D33">
-        <v>26.28</v>
+        <v>15.37</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H33">
-        <v>375</v>
+        <v>266</v>
       </c>
       <c r="I33">
-        <v>791</v>
+        <v>1448</v>
       </c>
       <c r="J33">
-        <v>3750</v>
+        <v>5838</v>
       </c>
       <c r="M33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N33">
-        <v>106</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O33">
-        <v>68.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="P33">
         <v>107.9</v>
@@ -1744,390 +1735,366 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B34">
-        <v>614.96</v>
+        <v>164.68</v>
       </c>
       <c r="C34">
-        <v>173.34</v>
+        <v>47.42</v>
       </c>
       <c r="D34">
-        <v>26.44</v>
+        <v>13.41</v>
       </c>
       <c r="G34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H34">
-        <v>146</v>
+        <v>313</v>
       </c>
       <c r="I34">
-        <v>619</v>
+        <v>1671</v>
       </c>
       <c r="J34">
-        <v>3763</v>
+        <v>6706</v>
       </c>
       <c r="M34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N34">
-        <v>43.9</v>
+        <v>67.7</v>
       </c>
       <c r="O34">
-        <v>80.3</v>
+        <v>89.7</v>
       </c>
       <c r="P34">
-        <v>103.3</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B35">
-        <v>513.42</v>
+        <v>81.13</v>
       </c>
       <c r="C35">
-        <v>138.08</v>
+        <v>35.71</v>
       </c>
       <c r="D35">
-        <v>22.01</v>
+        <v>12.77</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H35">
-        <v>187</v>
+        <v>364</v>
       </c>
       <c r="I35">
-        <v>766</v>
+        <v>1721</v>
       </c>
       <c r="J35">
-        <v>4485</v>
+        <v>6876</v>
       </c>
       <c r="M35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N35">
-        <v>64.7</v>
+        <v>65.5</v>
       </c>
       <c r="O35">
-        <v>153.8</v>
+        <v>74.7</v>
       </c>
       <c r="P35">
-        <v>88.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B36">
-        <v>383.14</v>
+        <v>101.53</v>
       </c>
       <c r="C36">
-        <v>116.57</v>
+        <v>43.78</v>
       </c>
       <c r="D36">
-        <v>20.86</v>
+        <v>12.34</v>
       </c>
       <c r="G36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H36">
-        <v>261</v>
+        <v>408</v>
       </c>
       <c r="I36">
-        <v>922</v>
+        <v>1800</v>
       </c>
       <c r="J36">
-        <v>4697</v>
+        <v>6802</v>
       </c>
       <c r="M36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N36">
-        <v>87.3</v>
+        <v>79.7</v>
       </c>
       <c r="O36">
-        <v>116</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="P36">
-        <v>79.3</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B37">
-        <v>473.13</v>
+        <v>134.37</v>
       </c>
       <c r="C37">
-        <v>112.16</v>
+        <v>34.62</v>
       </c>
       <c r="D37">
-        <v>20.9</v>
+        <v>10.21</v>
       </c>
       <c r="G37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H37">
-        <v>228</v>
+        <v>470</v>
       </c>
       <c r="I37">
-        <v>888</v>
+        <v>2104</v>
       </c>
       <c r="J37">
-        <v>4735</v>
+        <v>9424</v>
       </c>
       <c r="M37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N37">
-        <v>80.3</v>
+        <v>97.2</v>
       </c>
       <c r="O37">
-        <v>80.8</v>
+        <v>76.2</v>
       </c>
       <c r="P37">
-        <v>82.8</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B38">
-        <v>339.19</v>
+        <v>137.65</v>
       </c>
       <c r="C38">
-        <v>81.02</v>
+        <v>30.34</v>
       </c>
       <c r="D38">
-        <v>15.3</v>
+        <v>11.55</v>
       </c>
       <c r="G38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H38">
-        <v>312</v>
+        <v>434</v>
       </c>
       <c r="I38">
-        <v>1216</v>
+        <v>1904</v>
       </c>
       <c r="J38">
-        <v>6668</v>
+        <v>8162</v>
       </c>
       <c r="M38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N38">
-        <v>81.90000000000001</v>
+        <v>41.1</v>
       </c>
       <c r="O38">
-        <v>91.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P38">
-        <v>98.40000000000001</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B39">
-        <v>378.7</v>
+        <v>185.38</v>
       </c>
       <c r="C39">
-        <v>102.19</v>
+        <v>32.77</v>
       </c>
       <c r="D39">
-        <v>17.51</v>
+        <v>8.06</v>
       </c>
       <c r="G39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H39">
-        <v>276</v>
+        <v>518</v>
       </c>
       <c r="I39">
-        <v>1010</v>
+        <v>2590</v>
       </c>
       <c r="J39">
-        <v>5679</v>
+        <v>11126</v>
       </c>
       <c r="M39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N39">
-        <v>94.90000000000001</v>
+        <v>119.2</v>
       </c>
       <c r="O39">
-        <v>59.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P39">
-        <v>97.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B40">
-        <v>237.76</v>
+        <v>118.1</v>
       </c>
       <c r="C40">
-        <v>60.77</v>
+        <v>27.6</v>
       </c>
       <c r="D40">
-        <v>11.49</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H40">
-        <v>394</v>
+        <v>561</v>
       </c>
       <c r="I40">
-        <v>1633</v>
+        <v>2542</v>
       </c>
       <c r="J40">
-        <v>8550</v>
+        <v>11340</v>
       </c>
       <c r="M40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N40">
-        <v>44.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O40">
-        <v>83.3</v>
+        <v>104.1</v>
       </c>
       <c r="P40">
-        <v>96.40000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B41">
-        <v>232.25</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="C41">
-        <v>57.13</v>
+        <v>24.65</v>
       </c>
       <c r="D41">
-        <v>11.25</v>
+        <v>7.18</v>
       </c>
       <c r="G41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H41">
-        <v>389</v>
+        <v>606</v>
       </c>
       <c r="I41">
-        <v>1620</v>
+        <v>2843</v>
       </c>
       <c r="J41">
-        <v>8847</v>
+        <v>13258</v>
       </c>
       <c r="M41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N41">
-        <v>49.7</v>
+        <v>66.8</v>
       </c>
       <c r="O41">
-        <v>85.59999999999999</v>
+        <v>102</v>
       </c>
       <c r="P41">
-        <v>86.2</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B42">
-        <v>232.37</v>
+        <v>109.34</v>
       </c>
       <c r="C42">
-        <v>52.42</v>
+        <v>24.08</v>
       </c>
       <c r="D42">
-        <v>9.91</v>
+        <v>7.12</v>
       </c>
       <c r="G42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H42">
-        <v>422</v>
+        <v>640</v>
       </c>
       <c r="I42">
-        <v>1887</v>
+        <v>3181</v>
       </c>
       <c r="J42">
-        <v>10229</v>
+        <v>13521</v>
       </c>
       <c r="M42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N42">
-        <v>73.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="O42">
-        <v>83.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="P42">
-        <v>94.59999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43">
-        <v>174.19</v>
-      </c>
-      <c r="C43">
-        <v>47.94</v>
-      </c>
-      <c r="D43">
-        <v>9.65</v>
-      </c>
-      <c r="G43" t="s">
-        <v>90</v>
-      </c>
-      <c r="H43">
-        <v>542</v>
-      </c>
-      <c r="I43">
-        <v>2077</v>
-      </c>
-      <c r="J43">
-        <v>10282</v>
-      </c>
-      <c r="M43" t="s">
-        <v>90</v>
-      </c>
-      <c r="N43">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="O43">
-        <v>87.5</v>
-      </c>
-      <c r="P43">
-        <v>85.2</v>
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
       <c r="B49" t="s">
         <v>97</v>
       </c>
@@ -2150,20 +2117,6 @@
       </c>
       <c r="D50" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>104</v>
-      </c>
-      <c r="B51" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2173,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2193,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="K1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2201,7 +2154,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2210,7 +2163,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J2" t="s">
         <v>3</v>
@@ -2224,22 +2177,22 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>100.853</v>
+        <v>47.201</v>
       </c>
       <c r="C3">
-        <v>4.863025365314508E-05</v>
+        <v>0.0001048156180427262</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>5255</v>
+        <v>10376</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2247,22 +2200,22 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>92.404</v>
+        <v>44.308</v>
       </c>
       <c r="C4">
-        <v>0.0001533889159580629</v>
+        <v>0.0003271272196260645</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J4" t="s">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>2233</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2270,22 +2223,22 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>27.145</v>
+        <v>13.966</v>
       </c>
       <c r="C5">
-        <v>0.001286878775931299</v>
+        <v>0.002468794106336126</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J5" t="s">
         <v>6</v>
       </c>
       <c r="K5">
-        <v>2927</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2293,22 +2246,22 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>16.924</v>
+        <v>8.061999999999999</v>
       </c>
       <c r="C6">
-        <v>0.004384309656713109</v>
+        <v>0.0092583165224279</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J6" t="s">
         <v>7</v>
       </c>
       <c r="K6">
-        <v>1555</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2316,22 +2269,22 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>7.198</v>
+        <v>4.081</v>
       </c>
       <c r="C7">
-        <v>0.02098154246734712</v>
+        <v>0.03652684290068395</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J7" t="s">
         <v>8</v>
       </c>
       <c r="K7">
-        <v>1606</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2339,22 +2292,22 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>2.369</v>
+        <v>3.071</v>
       </c>
       <c r="C8">
-        <v>0.146475280673436</v>
+        <v>0.09766365524791647</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J8" t="s">
         <v>9</v>
       </c>
       <c r="K8">
-        <v>1820</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2362,22 +2315,22 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>11.208</v>
+        <v>24.801</v>
       </c>
       <c r="C9">
-        <v>0.06595828855999701</v>
+        <v>0.02832766224152289</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J9" t="s">
         <v>10</v>
       </c>
       <c r="K9">
-        <v>1044</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2385,22 +2338,22 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>9.654999999999999</v>
+        <v>19.478</v>
       </c>
       <c r="C10">
-        <v>0.1482566839255319</v>
+        <v>0.08154090595221969</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s">
         <v>11</v>
       </c>
       <c r="K10">
-        <v>774</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2408,22 +2361,22 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>18.804</v>
+        <v>96.739</v>
       </c>
       <c r="C11">
-        <v>0.1293810123320273</v>
+        <v>0.02684019448251886</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J11" t="s">
         <v>12</v>
       </c>
       <c r="K11">
-        <v>308</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2431,22 +2384,22 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>23.908</v>
+        <v>29.625</v>
       </c>
       <c r="C12">
-        <v>0.1609340032837405</v>
+        <v>0.1312066095475558</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J12" t="s">
         <v>13</v>
       </c>
       <c r="K12">
-        <v>321</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2454,22 +2407,22 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>37.265</v>
+        <v>31.033</v>
       </c>
       <c r="C13">
-        <v>0.1775663001869356</v>
+        <v>0.2357200422050705</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
       </c>
       <c r="K13">
-        <v>398</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2477,22 +2430,22 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>141.888</v>
+        <v>48.836</v>
       </c>
       <c r="C14">
-        <v>0.0895270991626787</v>
+        <v>0.2731482719260631</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
       <c r="K14">
-        <v>441</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2500,22 +2453,22 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>2462.204</v>
+        <v>906.486</v>
       </c>
       <c r="C15">
-        <v>0.009303301143244472</v>
+        <v>0.02566722706427625</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J15" t="s">
         <v>16</v>
       </c>
       <c r="K15">
-        <v>211</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2523,22 +2476,22 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>5580.473</v>
+        <v>3032.535</v>
       </c>
       <c r="C16">
-        <v>0.00674328065751523</v>
+        <v>0.01219953496979255</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
       <c r="K16">
-        <v>268</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2549,873 +2502,849 @@
         <v>12500</v>
       </c>
       <c r="C17">
-        <v>0.004000352677458857</v>
+        <v>0.003999999997924558</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
       </c>
       <c r="K17">
-        <v>839</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M21" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="B22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>272.94</v>
       </c>
       <c r="C23">
-        <v>111.7</v>
+        <v>194.72</v>
       </c>
       <c r="D23">
-        <v>51.43</v>
+        <v>571.14</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I23">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="J23">
-        <v>487</v>
+        <v>6</v>
       </c>
       <c r="M23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2657</v>
       </c>
       <c r="O23">
-        <v>6453.1</v>
+        <v>2656.3</v>
       </c>
       <c r="P23">
-        <v>8453.799999999999</v>
+        <v>3083.9</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B24">
-        <v>322.08</v>
+        <v>130.66</v>
       </c>
       <c r="C24">
-        <v>830.48</v>
+        <v>112.74</v>
       </c>
       <c r="D24">
-        <v>36460.53</v>
+        <v>68.47</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H24">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I24">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N24">
-        <v>4367.5</v>
+        <v>2533.7</v>
       </c>
       <c r="O24">
-        <v>7593.5</v>
+        <v>2433.9</v>
       </c>
       <c r="P24">
-        <v>663.3</v>
+        <v>3636.9</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B25">
-        <v>3228.14</v>
+        <v>177.49</v>
       </c>
       <c r="C25">
-        <v>361.29</v>
+        <v>83.31</v>
       </c>
       <c r="D25">
-        <v>122.73</v>
+        <v>17.66</v>
       </c>
       <c r="G25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H25">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="I25">
-        <v>62</v>
+        <v>177</v>
       </c>
       <c r="J25">
-        <v>129</v>
+        <v>749</v>
       </c>
       <c r="M25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N25">
-        <v>23424.7</v>
+        <v>2218.8</v>
       </c>
       <c r="O25">
-        <v>4086.4</v>
+        <v>3431.9</v>
       </c>
       <c r="P25">
-        <v>11591.7</v>
+        <v>6538.7</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B26">
-        <v>206.65</v>
+        <v>45.15</v>
       </c>
       <c r="C26">
-        <v>118.88</v>
+        <v>11.65</v>
       </c>
       <c r="D26">
-        <v>40.29</v>
+        <v>4.24</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H26">
-        <v>54</v>
+        <v>368</v>
       </c>
       <c r="I26">
-        <v>157</v>
+        <v>1099</v>
       </c>
       <c r="J26">
-        <v>522</v>
+        <v>3590</v>
       </c>
       <c r="M26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N26">
-        <v>5457.4</v>
+        <v>4619.3</v>
       </c>
       <c r="O26">
-        <v>8013.6</v>
+        <v>6267.9</v>
       </c>
       <c r="P26">
-        <v>9525.200000000001</v>
+        <v>8322.9</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B27">
-        <v>33.59</v>
+        <v>45.61</v>
       </c>
       <c r="C27">
-        <v>14.12</v>
+        <v>16.12</v>
       </c>
       <c r="D27">
-        <v>4.17</v>
+        <v>5.12</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H27">
-        <v>616</v>
+        <v>318</v>
       </c>
       <c r="I27">
-        <v>1335</v>
+        <v>940</v>
       </c>
       <c r="J27">
-        <v>4785</v>
+        <v>3031</v>
       </c>
       <c r="M27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N27">
-        <v>8451</v>
+        <v>3871.5</v>
       </c>
       <c r="O27">
-        <v>9320</v>
+        <v>8228.9</v>
       </c>
       <c r="P27">
-        <v>9724.799999999999</v>
+        <v>8440.200000000001</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28">
-        <v>41.48</v>
+        <v>30.58</v>
       </c>
       <c r="C28">
-        <v>16.57</v>
+        <v>14.18</v>
       </c>
       <c r="D28">
-        <v>5.82</v>
+        <v>4.36</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H28">
-        <v>521</v>
+        <v>374</v>
       </c>
       <c r="I28">
-        <v>1132</v>
+        <v>1017</v>
       </c>
       <c r="J28">
-        <v>3737</v>
+        <v>3227</v>
       </c>
       <c r="M28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N28">
-        <v>8413</v>
+        <v>5587.8</v>
       </c>
       <c r="O28">
-        <v>9836.5</v>
+        <v>4161.8</v>
       </c>
       <c r="P28">
-        <v>10508.5</v>
+        <v>7429.6</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B29">
-        <v>41.17</v>
+        <v>29.6</v>
       </c>
       <c r="C29">
-        <v>18.64</v>
+        <v>16.69</v>
       </c>
       <c r="D29">
-        <v>4.94</v>
+        <v>3.58</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H29">
-        <v>540</v>
+        <v>366</v>
       </c>
       <c r="I29">
-        <v>1043</v>
+        <v>1068</v>
       </c>
       <c r="J29">
-        <v>4150</v>
+        <v>3832</v>
       </c>
       <c r="M29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N29">
-        <v>9670.799999999999</v>
+        <v>3208</v>
       </c>
       <c r="O29">
-        <v>9793.9</v>
+        <v>4793.9</v>
       </c>
       <c r="P29">
-        <v>10193.1</v>
+        <v>8662.9</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B30">
-        <v>35.16</v>
+        <v>35.11</v>
       </c>
       <c r="C30">
-        <v>17.2</v>
+        <v>17.51</v>
       </c>
       <c r="D30">
-        <v>4.16</v>
+        <v>3.82</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H30">
-        <v>583</v>
+        <v>363</v>
       </c>
       <c r="I30">
-        <v>1232</v>
+        <v>1018</v>
       </c>
       <c r="J30">
-        <v>4813</v>
+        <v>3592</v>
       </c>
       <c r="M30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N30">
-        <v>10818</v>
+        <v>2588.6</v>
       </c>
       <c r="O30">
-        <v>9864.1</v>
+        <v>5735.2</v>
       </c>
       <c r="P30">
-        <v>9713.200000000001</v>
+        <v>8208.299999999999</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B31">
-        <v>43.01</v>
+        <v>27.5</v>
       </c>
       <c r="C31">
-        <v>15.67</v>
+        <v>13.62</v>
       </c>
       <c r="D31">
-        <v>4.46</v>
+        <v>4.7</v>
       </c>
       <c r="G31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H31">
-        <v>541</v>
+        <v>326</v>
       </c>
       <c r="I31">
-        <v>1138</v>
+        <v>1033</v>
       </c>
       <c r="J31">
-        <v>4421</v>
+        <v>3162</v>
       </c>
       <c r="M31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N31">
-        <v>8608.799999999999</v>
+        <v>3362.2</v>
       </c>
       <c r="O31">
-        <v>8944.799999999999</v>
+        <v>5491.5</v>
       </c>
       <c r="P31">
-        <v>9295.299999999999</v>
+        <v>8388.799999999999</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B32">
-        <v>57.91</v>
+        <v>40.58</v>
       </c>
       <c r="C32">
-        <v>20.64</v>
+        <v>14.17</v>
       </c>
       <c r="D32">
-        <v>4.8</v>
+        <v>4.16</v>
       </c>
       <c r="G32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H32">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="I32">
-        <v>1036</v>
+        <v>969</v>
       </c>
       <c r="J32">
-        <v>3913</v>
+        <v>3559</v>
       </c>
       <c r="M32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N32">
-        <v>9667.5</v>
+        <v>4086.2</v>
       </c>
       <c r="O32">
-        <v>9299.200000000001</v>
+        <v>5540.8</v>
       </c>
       <c r="P32">
-        <v>9148.5</v>
+        <v>8402.5</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B33">
-        <v>41.23</v>
+        <v>60.96</v>
       </c>
       <c r="C33">
-        <v>16.61</v>
+        <v>22.8</v>
       </c>
       <c r="D33">
-        <v>4.56</v>
+        <v>6.78</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H33">
-        <v>517</v>
+        <v>159</v>
       </c>
       <c r="I33">
-        <v>1046</v>
+        <v>694</v>
       </c>
       <c r="J33">
-        <v>4594</v>
+        <v>2147</v>
       </c>
       <c r="M33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N33">
-        <v>10362.1</v>
+        <v>3384.4</v>
       </c>
       <c r="O33">
-        <v>8996.9</v>
+        <v>4635.6</v>
       </c>
       <c r="P33">
-        <v>9694.5</v>
+        <v>7432.4</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B34">
-        <v>62.52</v>
+        <v>63.54</v>
       </c>
       <c r="C34">
-        <v>29.27</v>
+        <v>18.28</v>
       </c>
       <c r="D34">
-        <v>7.73</v>
+        <v>5.51</v>
       </c>
       <c r="G34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H34">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="I34">
-        <v>595</v>
+        <v>763</v>
       </c>
       <c r="J34">
-        <v>2592</v>
+        <v>2405</v>
       </c>
       <c r="M34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N34">
-        <v>6783.1</v>
+        <v>4336.8</v>
       </c>
       <c r="O34">
-        <v>9751.9</v>
+        <v>6136.3</v>
       </c>
       <c r="P34">
-        <v>9997.4</v>
+        <v>7571.1</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B35">
-        <v>73.41</v>
+        <v>35.89</v>
       </c>
       <c r="C35">
-        <v>28.56</v>
+        <v>16.84</v>
       </c>
       <c r="D35">
-        <v>6.36</v>
+        <v>4.88</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H35">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="I35">
-        <v>638</v>
+        <v>796</v>
       </c>
       <c r="J35">
-        <v>3079</v>
+        <v>2749</v>
       </c>
       <c r="M35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N35">
-        <v>9477.799999999999</v>
+        <v>2863.3</v>
       </c>
       <c r="O35">
-        <v>7435.1</v>
+        <v>5248.7</v>
       </c>
       <c r="P35">
-        <v>9315.200000000001</v>
+        <v>6265.4</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B36">
-        <v>69.68000000000001</v>
+        <v>40.19</v>
       </c>
       <c r="C36">
-        <v>24.14</v>
+        <v>14.78</v>
       </c>
       <c r="D36">
-        <v>5.77</v>
+        <v>5.1</v>
       </c>
       <c r="G36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H36">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="I36">
-        <v>801</v>
+        <v>869</v>
       </c>
       <c r="J36">
-        <v>3450</v>
+        <v>2865</v>
       </c>
       <c r="M36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N36">
-        <v>10186</v>
+        <v>2555</v>
       </c>
       <c r="O36">
-        <v>9271.9</v>
+        <v>5459.5</v>
       </c>
       <c r="P36">
-        <v>9393.200000000001</v>
+        <v>8692.9</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B37">
-        <v>69.3</v>
+        <v>37.03</v>
       </c>
       <c r="C37">
-        <v>23.74</v>
+        <v>19.23</v>
       </c>
       <c r="D37">
-        <v>5.41</v>
+        <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H37">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="I37">
-        <v>818</v>
+        <v>897</v>
       </c>
       <c r="J37">
-        <v>3559</v>
+        <v>2914</v>
       </c>
       <c r="M37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N37">
-        <v>9579.5</v>
+        <v>2524.6</v>
       </c>
       <c r="O37">
-        <v>9927.9</v>
+        <v>5420.1</v>
       </c>
       <c r="P37">
-        <v>10051.3</v>
+        <v>6558.5</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B38">
-        <v>39.08</v>
+        <v>29.87</v>
       </c>
       <c r="C38">
-        <v>21.35</v>
+        <v>17</v>
       </c>
       <c r="D38">
-        <v>5.44</v>
+        <v>4.18</v>
       </c>
       <c r="G38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H38">
-        <v>440</v>
+        <v>305</v>
       </c>
       <c r="I38">
-        <v>937</v>
+        <v>843</v>
       </c>
       <c r="J38">
-        <v>3661</v>
+        <v>3286</v>
       </c>
       <c r="M38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N38">
-        <v>8241.299999999999</v>
+        <v>3609.2</v>
       </c>
       <c r="O38">
-        <v>9588</v>
+        <v>6098.3</v>
       </c>
       <c r="P38">
-        <v>8821.299999999999</v>
+        <v>8715.200000000001</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B39">
-        <v>67.61</v>
+        <v>25.78</v>
       </c>
       <c r="C39">
-        <v>23.1</v>
+        <v>11.15</v>
       </c>
       <c r="D39">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="G39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H39">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I39">
-        <v>907</v>
+        <v>1108</v>
       </c>
       <c r="J39">
-        <v>3941</v>
+        <v>4067</v>
       </c>
       <c r="M39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N39">
-        <v>10779.6</v>
+        <v>4453.6</v>
       </c>
       <c r="O39">
-        <v>10341.5</v>
+        <v>6252.5</v>
       </c>
       <c r="P39">
-        <v>9387.4</v>
+        <v>7655.7</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B40">
-        <v>37.11</v>
+        <v>38.38</v>
       </c>
       <c r="C40">
-        <v>13.63</v>
+        <v>12.41</v>
       </c>
       <c r="D40">
-        <v>3.72</v>
+        <v>3.38</v>
       </c>
       <c r="G40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H40">
-        <v>501</v>
+        <v>323</v>
       </c>
       <c r="I40">
-        <v>1386</v>
+        <v>1106</v>
       </c>
       <c r="J40">
-        <v>5281</v>
+        <v>4362</v>
       </c>
       <c r="M40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N40">
-        <v>9258</v>
+        <v>3516.3</v>
       </c>
       <c r="O40">
-        <v>9952.4</v>
+        <v>5705.3</v>
       </c>
       <c r="P40">
-        <v>9222.299999999999</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B41">
-        <v>38.25</v>
+        <v>27.56</v>
       </c>
       <c r="C41">
-        <v>13.24</v>
+        <v>11.7</v>
       </c>
       <c r="D41">
-        <v>3.63</v>
+        <v>3.28</v>
       </c>
       <c r="G41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H41">
-        <v>521</v>
+        <v>404</v>
       </c>
       <c r="I41">
-        <v>1351</v>
+        <v>1252</v>
       </c>
       <c r="J41">
-        <v>5570</v>
+        <v>4550</v>
       </c>
       <c r="M41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N41">
-        <v>9708.6</v>
+        <v>5237.5</v>
       </c>
       <c r="O41">
-        <v>9191</v>
+        <v>5263.3</v>
       </c>
       <c r="P41">
-        <v>9294.799999999999</v>
+        <v>9359.6</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B42">
-        <v>27.41</v>
+        <v>30.25</v>
       </c>
       <c r="C42">
-        <v>13.06</v>
+        <v>10.31</v>
       </c>
       <c r="D42">
-        <v>3.43</v>
+        <v>3.07</v>
       </c>
       <c r="G42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H42">
-        <v>610</v>
+        <v>416</v>
       </c>
       <c r="I42">
-        <v>1484</v>
+        <v>1349</v>
       </c>
       <c r="J42">
-        <v>5911</v>
+        <v>4688</v>
       </c>
       <c r="M42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N42">
-        <v>8730.200000000001</v>
+        <v>4890.5</v>
       </c>
       <c r="O42">
-        <v>9263.299999999999</v>
+        <v>7188.7</v>
       </c>
       <c r="P42">
-        <v>9364.200000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43">
-        <v>27.71</v>
-      </c>
-      <c r="C43">
-        <v>11.75</v>
-      </c>
-      <c r="D43">
-        <v>3.16</v>
-      </c>
-      <c r="G43" t="s">
-        <v>90</v>
-      </c>
-      <c r="H43">
-        <v>626</v>
-      </c>
-      <c r="I43">
-        <v>1580</v>
-      </c>
-      <c r="J43">
-        <v>6085</v>
-      </c>
-      <c r="M43" t="s">
-        <v>90</v>
-      </c>
-      <c r="N43">
-        <v>8588.200000000001</v>
-      </c>
-      <c r="O43">
-        <v>9213.200000000001</v>
-      </c>
-      <c r="P43">
-        <v>9407.6</v>
+        <v>7429.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
       <c r="B49" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3423,27 +3352,13 @@
         <v>100</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>104</v>
-      </c>
-      <c r="B51" t="s">
-        <v>127</v>
-      </c>
-      <c r="C51" t="s">
-        <v>127</v>
-      </c>
-      <c r="D51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3453,7 +3368,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3473,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="K1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3481,7 +3396,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3490,7 +3405,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J2" t="s">
         <v>3</v>
@@ -3504,22 +3419,22 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>393.364</v>
+        <v>136.653</v>
       </c>
       <c r="C3">
-        <v>3.150989912474526E-06</v>
+        <v>8.905150083833823E-06</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>2358</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3527,22 +3442,22 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>357.741</v>
+        <v>152.151</v>
       </c>
       <c r="C4">
-        <v>1.005091849910972E-05</v>
+        <v>2.322093308981287E-05</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J4" t="s">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>1255</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3550,22 +3465,22 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>109.467</v>
+        <v>37.92</v>
       </c>
       <c r="C5">
-        <v>7.90469598269369E-05</v>
+        <v>0.0002280731053266854</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J5" t="s">
         <v>6</v>
       </c>
       <c r="K5">
-        <v>1681</v>
+        <v>556</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3573,22 +3488,22 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>59.953</v>
+        <v>20.788</v>
       </c>
       <c r="C6">
-        <v>0.0003137801412067857</v>
+        <v>0.0009089953611531021</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J6" t="s">
         <v>7</v>
       </c>
       <c r="K6">
-        <v>1011</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3596,22 +3511,22 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>26.319</v>
+        <v>7.624</v>
       </c>
       <c r="C7">
-        <v>0.001436273887950177</v>
+        <v>0.004969537971103749</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J7" t="s">
         <v>8</v>
       </c>
       <c r="K7">
-        <v>961</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3619,22 +3534,22 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>5.179</v>
+        <v>2.574</v>
       </c>
       <c r="C8">
-        <v>0.0177650050433625</v>
+        <v>0.03252545458485963</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J8" t="s">
         <v>9</v>
       </c>
       <c r="K8">
-        <v>1340</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3642,22 +3557,22 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>2.158</v>
+        <v>6.076</v>
       </c>
       <c r="C9">
-        <v>0.08505238099265171</v>
+        <v>0.02804013708644115</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J9" t="s">
         <v>10</v>
       </c>
       <c r="K9">
-        <v>1096</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3665,22 +3580,22 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>13.343</v>
+        <v>12.065</v>
       </c>
       <c r="C10">
-        <v>0.02142031775652466</v>
+        <v>0.02763124540214152</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J10" t="s">
         <v>11</v>
       </c>
       <c r="K10">
-        <v>1147</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3688,22 +3603,22 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>190.597</v>
+        <v>274.856</v>
       </c>
       <c r="C11">
-        <v>0.003464280418109135</v>
+        <v>0.002202644285591002</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J11" t="s">
         <v>12</v>
       </c>
       <c r="K11">
-        <v>604</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3711,22 +3626,22 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>15.163</v>
+        <v>41.953</v>
       </c>
       <c r="C12">
-        <v>0.05880130434709301</v>
+        <v>0.02299284971069137</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J12" t="s">
         <v>13</v>
       </c>
       <c r="K12">
-        <v>669</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3734,22 +3649,22 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>56.05</v>
+        <v>161.835</v>
       </c>
       <c r="C13">
-        <v>0.03775914058860998</v>
+        <v>0.01379764489643803</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
       </c>
       <c r="K13">
-        <v>666</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3757,22 +3672,22 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>25.873</v>
+        <v>32.796</v>
       </c>
       <c r="C14">
-        <v>0.1408883237658093</v>
+        <v>0.1119231387460624</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
       <c r="K14">
-        <v>591</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3780,22 +3695,22 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>33.682</v>
+        <v>40.897</v>
       </c>
       <c r="C15">
-        <v>0.183225499017951</v>
+        <v>0.15595254689213</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J15" t="s">
         <v>16</v>
       </c>
       <c r="K15">
-        <v>388</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3803,22 +3718,22 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>24.278</v>
+        <v>18.159</v>
       </c>
       <c r="C16">
-        <v>0.404781445172899</v>
+        <v>0.5537956058776237</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
       <c r="K16">
-        <v>547</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3829,873 +3744,849 @@
         <v>1250</v>
       </c>
       <c r="C17">
-        <v>0.01000311308247857</v>
+        <v>0.01000642997036488</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
       </c>
       <c r="K17">
-        <v>5686</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M21" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="B22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>152.68</v>
       </c>
       <c r="C23">
-        <v>30.1</v>
+        <v>61.61</v>
       </c>
       <c r="D23">
-        <v>13.53</v>
+        <v>14.68</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I23">
-        <v>630</v>
+        <v>143</v>
       </c>
       <c r="J23">
-        <v>1413</v>
+        <v>396</v>
       </c>
       <c r="M23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>12124.3</v>
       </c>
       <c r="O23">
-        <v>31446.2</v>
+        <v>55441.2</v>
       </c>
       <c r="P23">
-        <v>43067.1</v>
+        <v>48277.4</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24">
+        <v>128.38</v>
+      </c>
+      <c r="C24">
+        <v>58.05</v>
+      </c>
+      <c r="D24">
+        <v>8.02</v>
+      </c>
+      <c r="G24" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24">
         <v>71</v>
       </c>
-      <c r="B24">
-        <v>303.04</v>
-      </c>
-      <c r="C24">
-        <v>152.75</v>
-      </c>
-      <c r="D24">
-        <v>78.2</v>
-      </c>
-      <c r="G24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24">
-        <v>96</v>
-      </c>
       <c r="I24">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="J24">
-        <v>282</v>
+        <v>950</v>
       </c>
       <c r="M24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N24">
-        <v>23733.3</v>
+        <v>24721.6</v>
       </c>
       <c r="O24">
-        <v>47992</v>
+        <v>40339.9</v>
       </c>
       <c r="P24">
-        <v>63180.8</v>
+        <v>33538.5</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B25">
-        <v>180.35</v>
+        <v>40.54</v>
       </c>
       <c r="C25">
-        <v>73.19</v>
+        <v>9.66</v>
       </c>
       <c r="D25">
-        <v>30.55</v>
+        <v>3.67</v>
       </c>
       <c r="G25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H25">
-        <v>118</v>
+        <v>207</v>
       </c>
       <c r="I25">
-        <v>246</v>
+        <v>872</v>
       </c>
       <c r="J25">
-        <v>631</v>
+        <v>2126</v>
       </c>
       <c r="M25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N25">
-        <v>55331</v>
+        <v>30908</v>
       </c>
       <c r="O25">
-        <v>48073.1</v>
+        <v>33765</v>
       </c>
       <c r="P25">
-        <v>32267.4</v>
+        <v>40759.5</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B26">
-        <v>39.35</v>
+        <v>11.42</v>
       </c>
       <c r="C26">
-        <v>23.44</v>
+        <v>3.82</v>
       </c>
       <c r="D26">
-        <v>9.039999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H26">
-        <v>459</v>
+        <v>785</v>
       </c>
       <c r="I26">
-        <v>882</v>
+        <v>2184</v>
       </c>
       <c r="J26">
-        <v>2109</v>
+        <v>4526</v>
       </c>
       <c r="M26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N26">
-        <v>36169.2</v>
+        <v>32518.9</v>
       </c>
       <c r="O26">
-        <v>32361</v>
+        <v>42323.5</v>
       </c>
       <c r="P26">
-        <v>39638.6</v>
+        <v>40870.4</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B27">
-        <v>10.12</v>
+        <v>10.92</v>
       </c>
       <c r="C27">
-        <v>7.41</v>
+        <v>3.95</v>
       </c>
       <c r="D27">
-        <v>2.93</v>
+        <v>1.77</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H27">
-        <v>2015</v>
+        <v>688</v>
       </c>
       <c r="I27">
-        <v>3030</v>
+        <v>1967</v>
       </c>
       <c r="J27">
-        <v>6936</v>
+        <v>4051</v>
       </c>
       <c r="M27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N27">
-        <v>36397.5</v>
+        <v>32124.1</v>
       </c>
       <c r="O27">
-        <v>42462.8</v>
+        <v>35926.7</v>
       </c>
       <c r="P27">
-        <v>38164.7</v>
+        <v>41596.2</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28">
-        <v>10.75</v>
+        <v>10.02</v>
       </c>
       <c r="C28">
-        <v>7.68</v>
+        <v>4.05</v>
       </c>
       <c r="D28">
-        <v>3.12</v>
+        <v>1.76</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H28">
-        <v>1858</v>
+        <v>804</v>
       </c>
       <c r="I28">
-        <v>2722</v>
+        <v>2101</v>
       </c>
       <c r="J28">
-        <v>6145</v>
+        <v>4055</v>
       </c>
       <c r="M28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N28">
-        <v>43114.5</v>
+        <v>32078.6</v>
       </c>
       <c r="O28">
-        <v>44067.2</v>
+        <v>34789.8</v>
       </c>
       <c r="P28">
-        <v>34021.2</v>
+        <v>41810.2</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B29">
-        <v>10.47</v>
+        <v>12.62</v>
       </c>
       <c r="C29">
-        <v>8.01</v>
+        <v>4.19</v>
       </c>
       <c r="D29">
-        <v>3.28</v>
+        <v>1.76</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H29">
-        <v>1802</v>
+        <v>691</v>
       </c>
       <c r="I29">
-        <v>2565</v>
+        <v>1914</v>
       </c>
       <c r="J29">
-        <v>6107</v>
+        <v>3962</v>
       </c>
       <c r="M29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N29">
-        <v>35029.2</v>
+        <v>35817.8</v>
       </c>
       <c r="O29">
-        <v>41569.8</v>
+        <v>34162.9</v>
       </c>
       <c r="P29">
-        <v>42600.9</v>
+        <v>42895</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B30">
-        <v>11.53</v>
+        <v>10.21</v>
       </c>
       <c r="C30">
-        <v>7.58</v>
+        <v>3.77</v>
       </c>
       <c r="D30">
-        <v>3.17</v>
+        <v>1.73</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H30">
-        <v>1702</v>
+        <v>731</v>
       </c>
       <c r="I30">
-        <v>2576</v>
+        <v>2111</v>
       </c>
       <c r="J30">
-        <v>6146</v>
+        <v>4262</v>
       </c>
       <c r="M30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N30">
-        <v>33850.3</v>
+        <v>36854.9</v>
       </c>
       <c r="O30">
-        <v>33664.2</v>
+        <v>44496.7</v>
       </c>
       <c r="P30">
-        <v>35022.3</v>
+        <v>43204.5</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B31">
-        <v>11.54</v>
+        <v>11.95</v>
       </c>
       <c r="C31">
-        <v>7.78</v>
+        <v>3.77</v>
       </c>
       <c r="D31">
-        <v>3.24</v>
+        <v>1.81</v>
       </c>
       <c r="G31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H31">
-        <v>1784</v>
+        <v>729</v>
       </c>
       <c r="I31">
-        <v>2617</v>
+        <v>2105</v>
       </c>
       <c r="J31">
-        <v>6394</v>
+        <v>4156</v>
       </c>
       <c r="M31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N31">
-        <v>34969.6</v>
+        <v>43866.1</v>
       </c>
       <c r="O31">
-        <v>37617.4</v>
+        <v>36975</v>
       </c>
       <c r="P31">
-        <v>40407.3</v>
+        <v>41163</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B32">
-        <v>11.83</v>
+        <v>11.52</v>
       </c>
       <c r="C32">
-        <v>8.16</v>
+        <v>3.8</v>
       </c>
       <c r="D32">
-        <v>3.01</v>
+        <v>1.66</v>
       </c>
       <c r="G32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H32">
-        <v>1691</v>
+        <v>691</v>
       </c>
       <c r="I32">
-        <v>2563</v>
+        <v>2073</v>
       </c>
       <c r="J32">
-        <v>6252</v>
+        <v>4380</v>
       </c>
       <c r="M32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N32">
-        <v>39335.7</v>
+        <v>38929.9</v>
       </c>
       <c r="O32">
-        <v>33166.9</v>
+        <v>40856.2</v>
       </c>
       <c r="P32">
-        <v>34711.1</v>
+        <v>40503.7</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B33">
-        <v>12.57</v>
+        <v>18.87</v>
       </c>
       <c r="C33">
-        <v>7.84</v>
+        <v>5.16</v>
       </c>
       <c r="D33">
-        <v>3.28</v>
+        <v>2.15</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H33">
-        <v>1727</v>
+        <v>464</v>
       </c>
       <c r="I33">
-        <v>2611</v>
+        <v>1532</v>
       </c>
       <c r="J33">
-        <v>6357</v>
+        <v>3171</v>
       </c>
       <c r="M33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N33">
-        <v>43813.4</v>
+        <v>33159.1</v>
       </c>
       <c r="O33">
-        <v>41786.3</v>
+        <v>39105.3</v>
       </c>
       <c r="P33">
-        <v>42028</v>
+        <v>40834.4</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B34">
-        <v>22.44</v>
+        <v>22.19</v>
       </c>
       <c r="C34">
-        <v>14.83</v>
+        <v>4.74</v>
       </c>
       <c r="D34">
-        <v>5.4</v>
+        <v>2.03</v>
       </c>
       <c r="G34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H34">
-        <v>840</v>
+        <v>453</v>
       </c>
       <c r="I34">
-        <v>1443</v>
+        <v>1672</v>
       </c>
       <c r="J34">
-        <v>3691</v>
+        <v>3475</v>
       </c>
       <c r="M34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N34">
-        <v>32793</v>
+        <v>43558.2</v>
       </c>
       <c r="O34">
-        <v>37950.1</v>
+        <v>34938</v>
       </c>
       <c r="P34">
-        <v>43156.3</v>
+        <v>41167.7</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B35">
-        <v>20.46</v>
+        <v>18.97</v>
       </c>
       <c r="C35">
-        <v>12.88</v>
+        <v>4.65</v>
       </c>
       <c r="D35">
-        <v>5.12</v>
+        <v>1.9</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H35">
-        <v>873</v>
+        <v>561</v>
       </c>
       <c r="I35">
-        <v>1551</v>
+        <v>1778</v>
       </c>
       <c r="J35">
-        <v>4045</v>
+        <v>3680</v>
       </c>
       <c r="M35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N35">
-        <v>30408.2</v>
+        <v>36124</v>
       </c>
       <c r="O35">
-        <v>34209.2</v>
+        <v>39891.7</v>
       </c>
       <c r="P35">
-        <v>37435.1</v>
+        <v>40403.2</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B36">
-        <v>15.79</v>
+        <v>17.83</v>
       </c>
       <c r="C36">
-        <v>9.880000000000001</v>
+        <v>4.75</v>
       </c>
       <c r="D36">
-        <v>3.81</v>
+        <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H36">
-        <v>1249</v>
+        <v>563</v>
       </c>
       <c r="I36">
-        <v>2120</v>
+        <v>1685</v>
       </c>
       <c r="J36">
-        <v>5327</v>
+        <v>3581</v>
       </c>
       <c r="M36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N36">
-        <v>42871.5</v>
+        <v>40078.4</v>
       </c>
       <c r="O36">
-        <v>38109.7</v>
+        <v>40669.6</v>
       </c>
       <c r="P36">
-        <v>37028.6</v>
+        <v>37880.4</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B37">
-        <v>17.19</v>
+        <v>12.25</v>
       </c>
       <c r="C37">
-        <v>9.98</v>
+        <v>3.61</v>
       </c>
       <c r="D37">
-        <v>4.07</v>
+        <v>1.75</v>
       </c>
       <c r="G37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H37">
-        <v>1170</v>
+        <v>662</v>
       </c>
       <c r="I37">
-        <v>2036</v>
+        <v>2195</v>
       </c>
       <c r="J37">
-        <v>5185</v>
+        <v>4337</v>
       </c>
       <c r="M37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N37">
-        <v>36432.1</v>
+        <v>31519.6</v>
       </c>
       <c r="O37">
-        <v>41250</v>
+        <v>36050.1</v>
       </c>
       <c r="P37">
-        <v>39313.9</v>
+        <v>42173.9</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B38">
-        <v>12.37</v>
+        <v>13.51</v>
       </c>
       <c r="C38">
-        <v>8.15</v>
+        <v>3.96</v>
       </c>
       <c r="D38">
-        <v>2.84</v>
+        <v>1.9</v>
       </c>
       <c r="G38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H38">
-        <v>1578</v>
+        <v>663</v>
       </c>
       <c r="I38">
-        <v>2733</v>
+        <v>1979</v>
       </c>
       <c r="J38">
-        <v>7068</v>
+        <v>3839</v>
       </c>
       <c r="M38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N38">
-        <v>30841.5</v>
+        <v>31228.2</v>
       </c>
       <c r="O38">
-        <v>41173.7</v>
+        <v>36880.5</v>
       </c>
       <c r="P38">
-        <v>41091.9</v>
+        <v>37258.1</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B39">
-        <v>13.85</v>
+        <v>12.4</v>
       </c>
       <c r="C39">
-        <v>9.91</v>
+        <v>3.94</v>
       </c>
       <c r="D39">
-        <v>3.55</v>
+        <v>1.47</v>
       </c>
       <c r="G39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H39">
-        <v>1266</v>
+        <v>730</v>
       </c>
       <c r="I39">
-        <v>2083</v>
+        <v>2091</v>
       </c>
       <c r="J39">
-        <v>5323</v>
+        <v>4706</v>
       </c>
       <c r="M39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N39">
-        <v>37711.4</v>
+        <v>34577.3</v>
       </c>
       <c r="O39">
-        <v>39731.2</v>
+        <v>43088.4</v>
       </c>
       <c r="P39">
-        <v>37598.6</v>
+        <v>39573.4</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B40">
-        <v>11.38</v>
+        <v>11.19</v>
       </c>
       <c r="C40">
-        <v>7.3</v>
+        <v>3.96</v>
       </c>
       <c r="D40">
-        <v>2.86</v>
+        <v>1.71</v>
       </c>
       <c r="G40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H40">
-        <v>1648</v>
+        <v>746</v>
       </c>
       <c r="I40">
-        <v>2756</v>
+        <v>2066</v>
       </c>
       <c r="J40">
-        <v>7061</v>
+        <v>4423</v>
       </c>
       <c r="M40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N40">
-        <v>33312.2</v>
+        <v>40871</v>
       </c>
       <c r="O40">
-        <v>35746.2</v>
+        <v>41585.4</v>
       </c>
       <c r="P40">
-        <v>38175.1</v>
+        <v>45795.9</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B41">
-        <v>12.37</v>
+        <v>9.17</v>
       </c>
       <c r="C41">
-        <v>7.44</v>
+        <v>3.36</v>
       </c>
       <c r="D41">
-        <v>2.95</v>
+        <v>1.52</v>
       </c>
       <c r="G41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H41">
-        <v>1601</v>
+        <v>854</v>
       </c>
       <c r="I41">
-        <v>2779</v>
+        <v>2352</v>
       </c>
       <c r="J41">
-        <v>6889</v>
+        <v>5062</v>
       </c>
       <c r="M41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N41">
-        <v>33257.9</v>
+        <v>35917.6</v>
       </c>
       <c r="O41">
-        <v>39300.6</v>
+        <v>37952.8</v>
       </c>
       <c r="P41">
-        <v>39875.8</v>
+        <v>43154.7</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B42">
-        <v>11.33</v>
+        <v>9.32</v>
       </c>
       <c r="C42">
-        <v>6.06</v>
+        <v>3.21</v>
       </c>
       <c r="D42">
-        <v>2.31</v>
+        <v>1.43</v>
       </c>
       <c r="G42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H42">
-        <v>1958</v>
+        <v>841</v>
       </c>
       <c r="I42">
-        <v>3389</v>
+        <v>2613</v>
       </c>
       <c r="J42">
-        <v>8444</v>
+        <v>5206</v>
       </c>
       <c r="M42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N42">
-        <v>45386.6</v>
+        <v>45184</v>
       </c>
       <c r="O42">
-        <v>39072.9</v>
+        <v>40598.8</v>
       </c>
       <c r="P42">
-        <v>38554.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43">
-        <v>9.67</v>
-      </c>
-      <c r="C43">
-        <v>5.7</v>
-      </c>
-      <c r="D43">
-        <v>2.29</v>
-      </c>
-      <c r="G43" t="s">
-        <v>90</v>
-      </c>
-      <c r="H43">
-        <v>2088</v>
-      </c>
-      <c r="I43">
-        <v>3759</v>
-      </c>
-      <c r="J43">
-        <v>9224</v>
-      </c>
-      <c r="M43" t="s">
-        <v>90</v>
-      </c>
-      <c r="N43">
-        <v>38466.2</v>
-      </c>
-      <c r="O43">
-        <v>38083</v>
-      </c>
-      <c r="P43">
-        <v>40056.3</v>
+        <v>42360.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
       <c r="B49" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -4703,27 +4594,13 @@
         <v>100</v>
       </c>
       <c r="B50" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D50" t="s">
         <v>144</v>
-      </c>
-      <c r="C50" t="s">
-        <v>145</v>
-      </c>
-      <c r="D50" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>104</v>
-      </c>
-      <c r="B51" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>
